--- a/reports/devops-jobs-israel-2026-W36.xlsx
+++ b/reports/devops-jobs-israel-2026-W36.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="508">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-31T13:30:58</t>
+    <t xml:space="preserve">2026-09-01T11:32:38</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -366,6 +366,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
   </si>
   <si>
@@ -537,55 +552,340 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
-    <t xml:space="preserve">Checkmarx</t>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ControlUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4458835752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zipher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zipher-4460024752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4461576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4458897579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ControlUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Software Engineer - Chip Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-software-engineer-chip-design-at-nvidia-4441368534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Solo Role (Site Only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-solo-role-site-only-at-autobrains-technologies-4457485304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Production Engineer</t>
@@ -600,537 +900,285 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4459790058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devsecops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Limy AI</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 2115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
+  </si>
+  <si>
     <t xml:space="preserve">Discreet Company</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snatch UP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-snatch-up-4461068713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4458897579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Software Engineer - Chip Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-software-engineer-chip-design-at-nvidia-4441368534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Solo Role (Site Only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-solo-role-site-only-at-autobrains-technologies-4457485304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4458834488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-shavit-software-4461085347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPC Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-opc-energy-4459793105</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devsecops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-gong-4422913939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-cortex-at-palo-alto-networks-4428920772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 2115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-log-on-software-4457241389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client Facing System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarity Sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4455896777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPC Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-opc-energy-4459793105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wenrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1146,18 +1194,18 @@
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
@@ -1188,10 +1236,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7%</t>
+    <t xml:space="preserve">46.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1218,27 +1266,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
   </si>
   <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1248,6 +1284,18 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1260,16 +1308,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
     <t xml:space="preserve">Automation Student</t>
@@ -1293,9 +1344,6 @@
     <t xml:space="preserve">Upwind Security</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
   </si>
   <si>
@@ -1317,154 +1365,157 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+    <t xml:space="preserve">Operations Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441086540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOC Analyst Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/soc-analyst-tier-1-at-log-on-software-4459305422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+    <t xml:space="preserve">Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-youcc-technologies-ltd-4459214418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1616,7 +1667,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -1624,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1632,7 +1683,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -1640,7 +1691,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1040</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="10">
@@ -1712,7 +1763,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1720,7 +1771,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1739,36 +1790,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="B2" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="B3" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1776,7 +1827,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1795,119 +1846,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>477</v>
+        <v>396</v>
       </c>
       <c r="B4" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>380</v>
+        <v>494</v>
       </c>
       <c r="B5" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="B8" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B9" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>372</v>
+        <v>497</v>
       </c>
       <c r="B10" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="B11" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="B12" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>302</v>
+        <v>498</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>480</v>
+        <v>393</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>481</v>
+        <v>388</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1915,10 +1966,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1943,13 +1994,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2">
@@ -1957,13 +2008,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>14.8</v>
+        <v>15.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1972,34 +2023,34 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>34.8</v>
+        <v>40.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -2008,43 +2059,43 @@
         <v>2.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>36.9</v>
+        <v>34.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -2053,7 +2104,7 @@
         <v>16.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2065,8 +2116,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2137,7 +2188,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2169,7 +2220,7 @@
         <v>45</v>
       </c>
       <c r="J3" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -2201,7 +2252,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -2233,7 +2284,7 @@
         <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -2265,7 +2316,7 @@
         <v>40</v>
       </c>
       <c r="J6" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -2297,7 +2348,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2329,7 +2380,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -2361,7 +2412,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -2393,7 +2444,7 @@
         <v>74</v>
       </c>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2425,7 +2476,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2457,7 +2508,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
@@ -2489,7 +2540,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -2521,7 +2572,7 @@
         <v>90</v>
       </c>
       <c r="J14" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -2553,7 +2604,7 @@
         <v>94</v>
       </c>
       <c r="J15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2585,7 +2636,7 @@
         <v>83</v>
       </c>
       <c r="J16" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -2617,7 +2668,7 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -2649,7 +2700,7 @@
         <v>45</v>
       </c>
       <c r="J18" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -2681,7 +2732,7 @@
         <v>110</v>
       </c>
       <c r="J19" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2713,18 +2764,18 @@
         <v>94</v>
       </c>
       <c r="J20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>48</v>
@@ -2733,97 +2784,97 @@
         <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="J22" s="3">
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J23" s="3">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>42</v>
@@ -2838,24 +2889,24 @@
         <v>131</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="J24" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>42</v>
@@ -2870,27 +2921,27 @@
         <v>136</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="J25" s="3">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>140</v>
@@ -2905,7 +2956,7 @@
         <v>142</v>
       </c>
       <c r="J26" s="3">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
@@ -2916,7 +2967,7 @@
         <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>48</v>
@@ -2925,30 +2976,30 @@
         <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J27" s="3">
-        <v>85</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>48</v>
@@ -2957,33 +3008,33 @@
         <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="J28" s="3">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>37</v>
@@ -2998,10 +3049,10 @@
         <v>156</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -3012,49 +3063,51 @@
         <v>158</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>48</v>
+        <v>159</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="J30" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="G31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>164</v>
@@ -3063,21 +3116,21 @@
         <v>165</v>
       </c>
       <c r="J31" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>42</v>
@@ -3087,24 +3140,24 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>48</v>
@@ -3117,24 +3170,24 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="J33" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>48</v>
@@ -3147,27 +3200,27 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="J34" s="3">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>42</v>
@@ -3177,27 +3230,27 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>94</v>
       </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>42</v>
@@ -3207,24 +3260,24 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>48</v>
@@ -3237,24 +3290,24 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>48</v>
@@ -3267,24 +3320,24 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>48</v>
@@ -3300,21 +3353,21 @@
         <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="J39" s="3">
-        <v>64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>48</v>
@@ -3327,10 +3380,10 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="J40" s="3">
         <v>0</v>
@@ -3338,16 +3391,16 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>42</v>
@@ -3360,21 +3413,21 @@
         <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="J41" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>48</v>
@@ -3387,10 +3440,10 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3398,13 +3451,13 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>48</v>
@@ -3423,21 +3476,21 @@
         <v>79</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>52</v>
+        <v>202</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>37</v>
@@ -3447,13 +3500,13 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J44" s="3">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
@@ -3461,10 +3514,10 @@
         <v>52</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>48</v>
@@ -3477,13 +3530,13 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46">
@@ -3491,10 +3544,10 @@
         <v>52</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>48</v>
@@ -3507,30 +3560,30 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>209</v>
+        <v>94</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3540,54 +3593,54 @@
         <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>215</v>
+        <v>119</v>
       </c>
       <c r="J47" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>48</v>
+        <v>218</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>42</v>
@@ -3597,13 +3650,13 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3611,13 +3664,13 @@
         <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
@@ -3627,10 +3680,10 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="J50" s="3">
         <v>0</v>
@@ -3638,32 +3691,32 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>52</v>
+        <v>225</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -3671,13 +3724,13 @@
         <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>37</v>
@@ -3687,40 +3740,40 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J53" s="3">
         <v>1</v>
@@ -3728,13 +3781,13 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>229</v>
+        <v>52</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -3747,24 +3800,24 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="J54" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>48</v>
@@ -3777,60 +3830,60 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>235</v>
+        <v>74</v>
       </c>
       <c r="J55" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>239</v>
+        <v>48</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="J56" s="3">
-        <v>88</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3843,7 +3896,7 @@
         <v>244</v>
       </c>
       <c r="J57" s="3">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
@@ -3857,34 +3910,34 @@
         <v>247</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J58" s="3">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>48</v>
@@ -3897,27 +3950,27 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>42</v>
@@ -3927,24 +3980,24 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>48</v>
@@ -3957,43 +4010,43 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>94</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>262</v>
+        <v>40</v>
       </c>
       <c r="J62" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
@@ -4004,23 +4057,23 @@
         <v>264</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="J63" s="3">
         <v>43</v>
@@ -4028,46 +4081,46 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="C64" s="3" t="s">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="I64" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="J64" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
@@ -4077,27 +4130,27 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>275</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4110,7 +4163,7 @@
         <v>276</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="J66" s="3">
         <v>5</v>
@@ -4118,16 +4171,16 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4137,146 +4190,146 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>94</v>
+        <v>281</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J68" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>170</v>
+        <v>275</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>61</v>
+        <v>295</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>52</v>
+        <v>296</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="J71" s="3">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>245</v>
+        <v>300</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>293</v>
+        <v>203</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>48</v>
@@ -4284,18 +4337,20 @@
       <c r="E72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>262</v>
+        <v>94</v>
       </c>
       <c r="J72" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -4303,10 +4358,10 @@
         <v>52</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>48</v>
@@ -4319,116 +4374,116 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J74" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>302</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>52</v>
+        <v>314</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>48</v>
@@ -4436,32 +4491,34 @@
       <c r="E77" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="J77" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>42</v>
@@ -4471,24 +4528,24 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>307</v>
+        <v>119</v>
       </c>
       <c r="J78" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>48</v>
@@ -4501,27 +4558,27 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J79" s="3">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4531,24 +4588,24 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>48</v>
@@ -4557,150 +4614,150 @@
         <v>42</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>323</v>
+        <v>52</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>94</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>251</v>
+        <v>340</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="J85" s="3">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>332</v>
+        <v>166</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>334</v>
+        <v>172</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>48</v>
@@ -4713,211 +4770,211 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>336</v>
+        <v>246</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="J87" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>338</v>
+        <v>52</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>237</v>
+        <v>348</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>239</v>
+        <v>48</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>339</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>343</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>210</v>
+        <v>353</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>170</v>
+        <v>355</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="J90" s="3">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>350</v>
+        <v>94</v>
       </c>
       <c r="J91" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>317</v>
+        <v>175</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>318</v>
+        <v>48</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>94</v>
       </c>
       <c r="J92" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>355</v>
+        <v>203</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>37</v>
@@ -4927,147 +4984,149 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>357</v>
+        <v>166</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>358</v>
+        <v>227</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="J94" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="J95" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>161</v>
+        <v>368</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F97" s="3"/>
+      <c r="F97" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J97" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>42</v>
@@ -5077,17 +5136,137 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="J98" s="3">
-        <v>3</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J99" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J101" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J102"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5186,6 +5365,10 @@
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5193,8 +5376,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5227,13 +5410,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5241,37 +5424,37 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5279,18 +5462,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5298,18 +5481,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5317,7 +5500,7 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
@@ -5325,10 +5508,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5336,18 +5519,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>216</v>
+        <v>319</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5355,18 +5538,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>217</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>378</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>220</v>
+        <v>379</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5374,239 +5557,11 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5616,18 +5571,6 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5641,23 +5584,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5665,31 +5608,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5697,39 +5640,39 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -5737,7 +5680,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5745,7 +5688,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5753,7 +5696,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5761,7 +5704,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5783,7 +5726,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -5796,15 +5739,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>251</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5812,7 +5755,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5820,23 +5763,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>203</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>57</v>
+        <v>252</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5844,7 +5787,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5852,7 +5795,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5860,7 +5803,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5868,7 +5811,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5876,7 +5819,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5884,7 +5827,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5892,7 +5835,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5900,7 +5843,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5921,16 +5864,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -5980,13 +5923,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3">
-        <v>7.4</v>
+        <v>10.1</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5994,10 +5937,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -6008,10 +5951,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C7" s="3">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6022,10 +5965,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -6036,10 +5979,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C9" s="3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6050,7 +5993,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C10" s="3">
         <v>5.0</v>
@@ -6064,13 +6007,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="C11" s="3">
-        <v>4.8</v>
+        <v>4.0</v>
       </c>
       <c r="D11" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6078,13 +6021,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6092,10 +6035,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -6106,7 +6049,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6120,13 +6063,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>139</v>
+        <v>351</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6134,13 +6077,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6160,21 +6103,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3">
@@ -6182,10 +6125,10 @@
         <v>42</v>
       </c>
       <c r="B3" s="3">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
@@ -6193,10 +6136,10 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -6215,7 +6158,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
@@ -6223,15 +6166,15 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -6244,15 +6187,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>239</v>
+        <v>125</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6260,7 +6203,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>318</v>
+        <v>248</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6268,15 +6211,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>213</v>
+        <v>285</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6303,10 +6246,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6318,10 +6261,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6338,28 +6281,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>90</v>
@@ -6370,31 +6313,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>90</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4">
@@ -6402,31 +6345,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>408</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
@@ -6443,13 +6386,13 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3">
         <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
@@ -6466,28 +6409,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="F6" s="3">
         <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>94</v>
@@ -6498,31 +6441,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>430</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="F7" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>416</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -6530,31 +6473,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3">
         <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -6562,28 +6505,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>74</v>
@@ -6594,28 +6537,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="F10" s="3">
         <v>46</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>61</v>
@@ -6626,31 +6569,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="F11" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>160</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
@@ -6658,31 +6601,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>170</v>
+        <v>279</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F12" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>284</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -6690,31 +6633,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="F13" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>90</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14">
@@ -6722,31 +6665,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>446</v>
+        <v>175</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="F14" s="3">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -6754,31 +6697,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>202</v>
+        <v>465</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F15" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6786,31 +6729,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>452</v>
+        <v>208</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="F16" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>160</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17">
@@ -6818,31 +6761,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>265</v>
+        <v>473</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F17" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>262</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -6850,31 +6793,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>336</v>
+        <v>223</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F18" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19">
@@ -6882,31 +6825,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>479</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>463</v>
+        <v>204</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="F19" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>465</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
@@ -6914,31 +6857,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>158</v>
+        <v>483</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>467</v>
+        <v>168</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="F20" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>408</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -6946,31 +6889,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F21" s="3">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W36.xlsx
+++ b/reports/devops-jobs-israel-2026-W36.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01T11:32:38</t>
+    <t xml:space="preserve">2026-09-02T11:08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Days Open</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Architect</t>
+    <t xml:space="preserve">Devops Student</t>
   </si>
   <si>
     <t xml:space="preserve">Nice</t>
@@ -132,60 +132,51 @@
     <t xml:space="preserve">Raanana</t>
   </si>
   <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Docker, CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Docker, CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Platform Engineer</t>
   </si>
   <si>
@@ -390,7 +381,7 @@
     <t xml:space="preserve">2026-08-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Appsflyer</t>
@@ -399,18 +390,6 @@
     <t xml:space="preserve">Herzliya</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
   </si>
   <si>
@@ -552,6 +531,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4459558151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4460691360</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Engineer</t>
   </si>
   <si>
@@ -564,58 +570,478 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
   </si>
   <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wonderful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zipher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zipher-4460024752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Rehovot, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4458835752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zipher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zipher-4460024752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
   </si>
   <si>
-    <t xml:space="preserve">Guardio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4461576843</t>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limy AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 2115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4458897579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450175228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devsecops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
@@ -627,532 +1053,25 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4458897579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Software Engineer - Chip Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-software-engineer-chip-design-at-nvidia-4441368534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Solo Role (Site Only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-solo-role-site-only-at-autobrains-technologies-4457485304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4459790058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devsecops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wenrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limy AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 2115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4458834488</t>
   </si>
   <si>
-    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
   </si>
   <si>
     <t xml:space="preserve">Senior System Engineer</t>
@@ -1167,18 +1086,21 @@
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
     <t xml:space="preserve">OPC Energy</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-opc-energy-4459793105</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1194,27 +1116,27 @@
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open Roles</t>
   </si>
   <si>
@@ -1236,10 +1158,7 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5%</t>
+    <t xml:space="preserve">50.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1251,63 +1170,54 @@
     <t xml:space="preserve">Stack</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMIT Offshore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, GCP, Cloud (any), Networking, Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -1323,6 +1233,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
@@ -1338,16 +1266,16 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
@@ -1365,31 +1293,43 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Operator</t>
@@ -1425,73 +1365,55 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441086540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-youcc-technologies-ltd-4459214418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1500,22 +1422,25 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
+    <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1667,7 +1592,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -1675,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1683,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1763,7 +1688,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1771,7 +1696,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1790,36 +1715,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="B2" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1827,7 +1752,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1846,39 +1771,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>493</v>
+        <v>371</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>396</v>
+        <v>467</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="B5" s="3">
         <v>16</v>
@@ -1886,47 +1811,47 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>286</v>
+        <v>366</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="B9" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="B11" s="3">
         <v>6</v>
@@ -1934,7 +1859,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>307</v>
+        <v>472</v>
       </c>
       <c r="B12" s="3">
         <v>6</v>
@@ -1942,23 +1867,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>498</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>388</v>
+        <v>473</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1966,7 +1891,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>390</v>
+        <v>309</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -1994,13 +1919,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2">
@@ -2008,13 +1933,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2023,88 +1948,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.2</v>
+        <v>34.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.9</v>
+        <v>18.1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.2</v>
+        <v>21.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2117,7 +2042,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2188,7 +2113,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -2196,48 +2121,48 @@
         <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>49</v>
@@ -2252,7 +2177,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>90</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -2260,144 +2185,144 @@
         <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="J8" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>69</v>
@@ -2409,39 +2334,39 @@
         <v>70</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J10" s="3">
         <v>2</v>
@@ -2449,51 +2374,51 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>81</v>
@@ -2508,103 +2433,103 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>79</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J15" s="3">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -2612,63 +2537,63 @@
         <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="J16" s="3">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2676,16 +2601,16 @@
         <v>104</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>105</v>
@@ -2697,91 +2622,91 @@
         <v>106</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="J18" s="3">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="J19" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="J20" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>117</v>
@@ -2796,332 +2721,328 @@
         <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J22" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="J23" s="3">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J24" s="3">
-        <v>20</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="J25" s="3">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J26" s="3">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="D27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="J27" s="3">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="J28" s="3">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="J29" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="J31" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>167</v>
@@ -3130,10 +3051,10 @@
         <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
@@ -3143,127 +3064,127 @@
         <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="J32" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="J36" s="3">
         <v>6</v>
@@ -3271,119 +3192,119 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="J40" s="3">
         <v>0</v>
@@ -3391,46 +3312,46 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="J41" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>37</v>
@@ -3443,10 +3364,10 @@
         <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -3457,10 +3378,10 @@
         <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>37</v>
@@ -3473,24 +3394,24 @@
         <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>37</v>
@@ -3500,27 +3421,27 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="J44" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>37</v>
@@ -3530,27 +3451,27 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J45" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>37</v>
@@ -3560,57 +3481,57 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>119</v>
+        <v>213</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>37</v>
@@ -3620,60 +3541,60 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="J48" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>166</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
@@ -3683,67 +3604,67 @@
         <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J51" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="J52" s="3">
         <v>1</v>
@@ -3751,19 +3672,19 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3773,57 +3694,57 @@
         <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>166</v>
+        <v>47</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3833,7 +3754,7 @@
         <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J55" s="3">
         <v>2</v>
@@ -3841,16 +3762,16 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3863,144 +3784,144 @@
         <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="J56" s="3">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>241</v>
+        <v>47</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J57" s="3">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>247</v>
+        <v>165</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>248</v>
+        <v>43</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="J58" s="3">
-        <v>89</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>251</v>
+        <v>47</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>257</v>
+        <v>159</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>37</v>
@@ -4010,147 +3931,147 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J61" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>40</v>
+        <v>255</v>
       </c>
       <c r="J62" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>266</v>
+        <v>51</v>
       </c>
       <c r="J63" s="3">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>270</v>
+        <v>46</v>
       </c>
       <c r="J64" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>271</v>
+        <v>47</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>273</v>
+        <v>168</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>61</v>
+        <v>264</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>275</v>
+        <v>168</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4160,425 +4081,421 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>94</v>
+        <v>255</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="J67" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>288</v>
+        <v>46</v>
       </c>
       <c r="J68" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>290</v>
+        <v>175</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>292</v>
+        <v>91</v>
       </c>
       <c r="J69" s="3">
-        <v>65</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="J70" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="J71" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>203</v>
+        <v>289</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>175</v>
+        <v>290</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>301</v>
-      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="J72" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>52</v>
+        <v>292</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="J73" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>307</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>310</v>
+        <v>175</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="J75" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="J76" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>316</v>
-      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>319</v>
+        <v>250</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F78" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="J79" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>327</v>
+        <v>168</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4588,59 +4505,59 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>94</v>
+        <v>317</v>
       </c>
       <c r="J80" s="3">
-        <v>5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>37</v>
@@ -4650,404 +4567,406 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="J82" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>336</v>
+        <v>47</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="J84" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>340</v>
+        <v>210</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>342</v>
+        <v>71</v>
       </c>
       <c r="J85" s="3">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>248</v>
+        <v>132</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>346</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>52</v>
+        <v>334</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="D88" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="J88" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>350</v>
+        <v>47</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>351</v>
+        <v>260</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>279</v>
+        <v>168</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>94</v>
+        <v>337</v>
       </c>
       <c r="J89" s="3">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="D90" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>357</v>
+        <v>230</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J91" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D92" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>301</v>
-      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>203</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="J93" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>166</v>
+        <v>348</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>227</v>
+        <v>349</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="J95" s="3">
         <v>1</v>
@@ -5055,16 +4974,16 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>58</v>
+        <v>356</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>37</v>
@@ -5074,199 +4993,47 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="J96" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>286</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J97" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J98" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J99" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J102" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J97"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5364,11 +5131,6 @@
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5377,7 +5139,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5410,13 +5172,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5424,18 +5186,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5443,18 +5205,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5462,18 +5224,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5481,18 +5243,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5500,18 +5262,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>259</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5519,18 +5281,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>318</v>
+        <v>273</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>319</v>
+        <v>274</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5538,18 +5300,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>320</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>378</v>
+        <v>159</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5557,11 +5319,87 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>380</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5571,6 +5409,10 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5584,55 +5426,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5640,39 +5482,39 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -5680,23 +5522,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5704,7 +5546,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5726,12 +5568,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -5739,7 +5581,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
         <v>3</v>
@@ -5747,7 +5589,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5755,7 +5597,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5763,7 +5605,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5771,7 +5613,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5779,7 +5621,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5787,7 +5629,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5795,7 +5637,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5803,7 +5645,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5811,7 +5653,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5819,7 +5661,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5827,7 +5669,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5835,7 +5677,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5843,7 +5685,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5864,16 +5706,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
@@ -5881,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3">
         <v>23.0</v>
@@ -5895,7 +5737,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3">
         <v>10.9</v>
@@ -5909,7 +5751,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C4" s="3">
         <v>10.4</v>
@@ -5923,7 +5765,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -5937,7 +5779,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3">
         <v>7.4</v>
@@ -5951,7 +5793,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3">
         <v>6.7</v>
@@ -5965,10 +5807,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="C8" s="3">
-        <v>6.2</v>
+        <v>5.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -5979,13 +5821,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C9" s="3">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5993,13 +5835,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>149</v>
+        <v>293</v>
       </c>
       <c r="C10" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6007,13 +5849,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C11" s="3">
-        <v>4.0</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6021,13 +5863,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6035,10 +5877,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -6049,7 +5891,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6063,7 +5905,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -6077,7 +5919,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6103,43 +5945,43 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -6158,23 +6000,23 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -6182,12 +6024,12 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6195,15 +6037,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6211,17 +6053,9 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>285</v>
+        <v>122</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6233,8 +6067,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6246,10 +6080,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6261,10 +6095,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6281,31 +6115,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>273</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>90</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3">
@@ -6313,31 +6147,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>420</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
@@ -6345,31 +6179,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>424</v>
+        <v>396</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -6377,7 +6211,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>34</v>
@@ -6386,22 +6220,22 @@
         <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="F5" s="3">
         <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -6409,31 +6243,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="F6" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -6441,31 +6275,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>175</v>
+        <v>406</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="F7" s="3">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>79</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8">
@@ -6473,31 +6307,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="F8" s="3">
         <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6505,31 +6339,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -6537,31 +6371,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="F10" s="3">
         <v>46</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -6569,31 +6403,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>448</v>
+        <v>354</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>450</v>
+        <v>222</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="F11" s="3">
         <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -6601,31 +6435,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>279</v>
+        <v>429</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="F12" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6633,31 +6467,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F13" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
@@ -6665,31 +6499,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F14" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
@@ -6697,31 +6531,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>273</v>
+        <v>168</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="F15" s="3">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -6729,31 +6563,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>208</v>
+        <v>445</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="F16" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>270</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -6761,31 +6595,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>471</v>
+        <v>437</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>472</v>
+        <v>228</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>473</v>
+        <v>161</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18">
@@ -6793,31 +6627,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>223</v>
+        <v>451</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>168</v>
+        <v>270</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="F18" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>165</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19">
@@ -6825,31 +6659,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="F19" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>90</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20">
@@ -6857,31 +6691,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>168</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>484</v>
+        <v>401</v>
       </c>
       <c r="F20" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>79</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21">
@@ -6889,31 +6723,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="F21" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>40</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W36.xlsx
+++ b/reports/devops-jobs-israel-2026-W36.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02T11:08:28</t>
+    <t xml:space="preserve">2026-09-03T11:05:02</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -498,636 +498,648 @@
     <t xml:space="preserve">2026-08-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-group-4460483664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 2115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zipher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zipher-4460024752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4461576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4458847873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wonderful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4459558151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4459790058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devsecops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-gong-4422913939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluevine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-bluevine-4460472346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limy AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
+  </si>
+  <si>
     <t xml:space="preserve">Scytale</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-06</t>
   </si>
   <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4458847873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4459558151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4459946559</t>
   </si>
   <si>
     <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4460691360</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ControlUp</t>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Data Infrastructure Engineer-2572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/big-data-infrastructure-engineer-2572-at-shabak-israeli-security-agency-career-4460456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
   </si>
   <si>
     <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wonderful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zipher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zipher-4460024752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limy AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 2115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4458897579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450175228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wenrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devsecops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Software Engineer - Chip Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-software-engineer-chip-design-at-nvidia-4441379111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4458834488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-shavit-software-4461085347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPC Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-opc-energy-4459793105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
@@ -1158,7 +1170,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0%</t>
+    <t xml:space="preserve">49.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1170,15 +1185,42 @@
     <t xml:space="preserve">Stack</t>
   </si>
   <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1200,24 +1242,36 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMMIT Offshore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
   </si>
   <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -1233,24 +1287,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
@@ -1266,16 +1302,43 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
@@ -1320,30 +1383,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -1353,67 +1398,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1592,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
@@ -1600,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1608,7 +1623,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -1616,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1027</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="10">
@@ -1688,7 +1703,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -1715,44 +1730,44 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1771,15 +1786,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B2" s="3">
         <v>29</v>
@@ -1787,7 +1802,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -1795,55 +1810,55 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>346</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>366</v>
+        <v>474</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>470</v>
+        <v>369</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>471</v>
+        <v>367</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -1851,50 +1866,50 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B11" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>477</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B14" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>473</v>
+        <v>348</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>309</v>
+        <v>478</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1919,13 +1934,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
@@ -1936,10 +1951,10 @@
         <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1948,88 +1963,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>38.8</v>
+        <v>36.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.7</v>
+        <v>29.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.1</v>
+        <v>14.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.4</v>
+        <v>19.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2040,8 +2055,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2113,7 +2128,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -2145,7 +2160,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2177,7 +2192,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -2209,7 +2224,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -2241,7 +2256,7 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2273,7 +2288,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2305,7 +2320,7 @@
         <v>51</v>
       </c>
       <c r="J8" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -2337,7 +2352,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2369,7 +2384,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2401,7 +2416,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -2433,7 +2448,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -2465,7 +2480,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -2497,7 +2512,7 @@
         <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -2529,7 +2544,7 @@
         <v>80</v>
       </c>
       <c r="J15" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -2561,7 +2576,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -2593,7 +2608,7 @@
         <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2625,7 +2640,7 @@
         <v>107</v>
       </c>
       <c r="J18" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2657,7 +2672,7 @@
         <v>91</v>
       </c>
       <c r="J19" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2689,7 +2704,7 @@
         <v>116</v>
       </c>
       <c r="J20" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2721,7 +2736,7 @@
         <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -2753,7 +2768,7 @@
         <v>125</v>
       </c>
       <c r="J22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -2785,7 +2800,7 @@
         <v>62</v>
       </c>
       <c r="J23" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -2817,7 +2832,7 @@
         <v>135</v>
       </c>
       <c r="J24" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
@@ -2849,7 +2864,7 @@
         <v>140</v>
       </c>
       <c r="J25" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -2881,7 +2896,7 @@
         <v>146</v>
       </c>
       <c r="J26" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
@@ -2913,7 +2928,7 @@
         <v>51</v>
       </c>
       <c r="J27" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -2945,7 +2960,7 @@
         <v>76</v>
       </c>
       <c r="J28" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2977,34 +2992,34 @@
         <v>158</v>
       </c>
       <c r="J29" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="J30" s="3">
         <v>27</v>
@@ -3012,13 +3027,13 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>43</v>
@@ -3031,24 +3046,24 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="J31" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>43</v>
@@ -3061,27 +3076,27 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J32" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>37</v>
@@ -3091,27 +3106,27 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="J33" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>37</v>
@@ -3121,144 +3136,144 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>183</v>
+        <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>43</v>
@@ -3271,24 +3286,24 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="J39" s="3">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>43</v>
@@ -3301,60 +3316,60 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3364,21 +3379,21 @@
         <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="J42" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>43</v>
@@ -3391,24 +3406,24 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>43</v>
@@ -3421,10 +3436,10 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="J44" s="3">
         <v>1</v>
@@ -3432,103 +3447,103 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J45" s="3">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>43</v>
+        <v>209</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="J47" s="3">
-        <v>89</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>43</v>
@@ -3541,84 +3556,84 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>223</v>
+        <v>43</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J50" s="3">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>43</v>
@@ -3631,163 +3646,165 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>161</v>
+        <v>226</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>132</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>47</v>
+        <v>233</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="D55" s="3" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="J55" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>71</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3795,13 +3812,13 @@
         <v>47</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>48</v>
@@ -3811,84 +3828,84 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>242</v>
+        <v>46</v>
       </c>
       <c r="J57" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="J58" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>47</v>
+        <v>247</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>168</v>
+        <v>245</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>91</v>
+        <v>250</v>
       </c>
       <c r="J59" s="3">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>43</v>
@@ -3901,54 +3918,54 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="J60" s="3">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>76</v>
+        <v>256</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>43</v>
@@ -3961,57 +3978,57 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>255</v>
+        <v>51</v>
       </c>
       <c r="J62" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>51</v>
+        <v>256</v>
       </c>
       <c r="J63" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>48</v>
@@ -4021,13 +4038,13 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="J64" s="3">
         <v>46</v>
-      </c>
-      <c r="J64" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4035,10 +4052,10 @@
         <v>47</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>43</v>
@@ -4051,24 +4068,24 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>264</v>
+        <v>169</v>
       </c>
       <c r="J65" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>43</v>
@@ -4081,90 +4098,90 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="J66" s="3">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>272</v>
+        <v>46</v>
       </c>
       <c r="J67" s="3">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>195</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>276</v>
+        <v>43</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>46</v>
+        <v>218</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>278</v>
+        <v>163</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
@@ -4174,10 +4191,10 @@
         <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="J69" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -4188,7 +4205,7 @@
         <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>132</v>
@@ -4201,43 +4218,43 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>168</v>
+        <v>286</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>287</v>
+        <v>205</v>
       </c>
       <c r="J71" s="3">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
@@ -4248,72 +4265,70 @@
         <v>289</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>290</v>
+        <v>172</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>132</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="J72" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>292</v>
+        <v>163</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>294</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>37</v>
@@ -4323,54 +4338,54 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>76</v>
+        <v>295</v>
       </c>
       <c r="J74" s="3">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>175</v>
+        <v>297</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>301</v>
+        <v>107</v>
       </c>
       <c r="J75" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>168</v>
+        <v>245</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>43</v>
@@ -4378,32 +4393,34 @@
       <c r="E76" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="J76" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="C77" s="3" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>37</v>
@@ -4413,24 +4430,24 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>307</v>
+        <v>116</v>
       </c>
       <c r="J77" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>43</v>
@@ -4439,60 +4456,60 @@
         <v>37</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>43</v>
@@ -4505,86 +4522,84 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J80" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>294</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>43</v>
@@ -4592,20 +4607,18 @@
       <c r="E83" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>324</v>
-      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4613,13 +4626,13 @@
         <v>47</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>48</v>
@@ -4629,42 +4642,40 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>328</v>
+        <v>163</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>210</v>
+        <v>324</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>329</v>
-      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J85" s="3">
         <v>3</v>
@@ -4672,149 +4683,149 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>132</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="J87" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>334</v>
+        <v>163</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>293</v>
+        <v>241</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>276</v>
+        <v>36</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="J88" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>260</v>
+        <v>332</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J89" s="3">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>275</v>
+        <v>337</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>276</v>
+        <v>132</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="J90" s="3">
         <v>23</v>
@@ -4822,49 +4833,51 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>159</v>
+        <v>339</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>230</v>
+        <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F91" s="3"/>
+      <c r="F91" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>341</v>
+        <v>163</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D92" s="3" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
@@ -4874,10 +4887,10 @@
         <v>343</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J92" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4888,7 +4901,7 @@
         <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>132</v>
@@ -4896,124 +4909,124 @@
       <c r="E93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>347</v>
-      </c>
       <c r="I93" s="3" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="J93" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>349</v>
+        <v>251</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="C95" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>132</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>358</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>165</v>
+        <v>359</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>37</v>
@@ -5023,17 +5036,47 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J97" s="3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J98" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J98"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5131,6 +5174,7 @@
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5138,8 +5182,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5172,32 +5216,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5205,18 +5249,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5224,18 +5268,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>191</v>
+        <v>268</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5243,18 +5287,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>192</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>199</v>
+        <v>309</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5262,18 +5306,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>201</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5281,18 +5325,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>261</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>273</v>
+        <v>339</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5300,18 +5344,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>277</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>159</v>
+        <v>350</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5319,18 +5363,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>361</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>326</v>
+        <v>182</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5338,68 +5382,11 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5410,9 +5397,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5426,15 +5410,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -5442,7 +5426,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5450,7 +5434,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="B4" s="3">
         <v>19</v>
@@ -5458,7 +5442,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -5466,7 +5450,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -5474,7 +5458,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5482,7 +5466,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5490,7 +5474,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5498,7 +5482,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5506,7 +5490,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>346</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5514,15 +5498,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>128</v>
+        <v>372</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5530,7 +5514,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5538,7 +5522,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5546,7 +5530,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5568,7 +5552,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5581,23 +5565,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5605,7 +5589,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5613,7 +5597,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>293</v>
+        <v>109</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5645,7 +5629,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5653,7 +5637,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5661,7 +5645,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5669,7 +5653,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5677,7 +5661,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5685,10 +5669,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5706,16 +5690,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5807,13 +5791,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -5821,13 +5805,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5835,13 +5819,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>293</v>
+        <v>142</v>
       </c>
       <c r="C10" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5849,7 +5833,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C11" s="3">
         <v>2.9</v>
@@ -5863,7 +5847,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5877,7 +5861,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5891,13 +5875,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>282</v>
+        <v>121</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5905,13 +5889,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>326</v>
+        <v>137</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5919,13 +5903,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5945,21 +5929,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3">
@@ -5970,7 +5954,7 @@
         <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4">
@@ -5978,10 +5962,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6000,7 +5984,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -6008,7 +5992,7 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -6024,20 +6008,20 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6045,7 +6029,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6067,8 +6051,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6080,10 +6064,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6095,10 +6079,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6115,31 +6099,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>388</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -6147,31 +6131,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -6179,31 +6163,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>116</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5">
@@ -6211,31 +6195,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>403</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>404</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>39</v>
+        <v>406</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
@@ -6243,31 +6227,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F6" s="3">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -6275,31 +6259,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>404</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>405</v>
+        <v>34</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>406</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F7" s="3">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>408</v>
+        <v>39</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>409</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -6307,31 +6291,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>168</v>
+        <v>414</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>414</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -6339,31 +6323,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="F9" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -6371,31 +6355,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="F10" s="3">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>58</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11">
@@ -6403,31 +6387,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>222</v>
+        <v>428</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6435,31 +6419,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>429</v>
+        <v>245</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="F12" s="3">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -6467,31 +6451,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>255</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14">
@@ -6499,31 +6483,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="F14" s="3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -6531,31 +6515,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>437</v>
+        <v>357</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F15" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -6563,31 +6547,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>173</v>
+        <v>450</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>385</v>
+        <v>451</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>76</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17">
@@ -6595,31 +6579,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>437</v>
+        <v>357</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>161</v>
+        <v>359</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F17" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>449</v>
+        <v>360</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>158</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -6627,31 +6611,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F18" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>307</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -6659,31 +6643,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>451</v>
+        <v>212</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="F19" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20">
@@ -6691,31 +6675,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>168</v>
+        <v>464</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="F20" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>255</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
@@ -6723,31 +6707,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>461</v>
+        <v>275</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>275</v>
+        <v>55</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F21" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>464</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W36.xlsx
+++ b/reports/devops-jobs-israel-2026-W36.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-03T11:05:02</t>
+    <t xml:space="preserve">2026-09-04T11:06:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -510,15 +510,33 @@
     <t xml:space="preserve">2026-08-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-upwind-security-4462845714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
     <t xml:space="preserve">Moveo Group</t>
   </si>
   <si>
@@ -561,18 +579,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zipher-4460024752</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
     <t xml:space="preserve">Guardio</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4461576843</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
   </si>
   <si>
@@ -603,10 +621,199 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wonderful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4458897579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
@@ -615,52 +822,130 @@
     <t xml:space="preserve">Petah Tikva</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wonderful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limy AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devsecops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
   </si>
   <si>
     <t xml:space="preserve">Sentra</t>
@@ -669,199 +954,112 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
   </si>
   <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
+    <t xml:space="preserve">Senior DevOps/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comblack-4462839099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-comblack-4462835218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
   </si>
   <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37483)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37483-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4462855334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/splunk-infrastructure-engineer-at-one-technologies-4460496741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-shavit-software-4461085347</t>
   </si>
   <si>
     <t xml:space="preserve">SRE Tech Lead</t>
@@ -876,15 +1074,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
   </si>
   <si>
@@ -894,222 +1083,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4459558151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wenrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4459790058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devsecops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-gong-4422913939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bluevine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-bluevine-4460472346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limy AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scytale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4459946559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4460691360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Data Infrastructure Engineer-2572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shabak - Israeli Security Agency - Career</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/big-data-infrastructure-engineer-2572-at-shabak-israeli-security-agency-career-4460456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Software Engineer - Chip Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-software-engineer-chip-design-at-nvidia-4441379111</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1170,10 +1143,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5%</t>
+    <t xml:space="preserve">48.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1200,76 +1173,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
   </si>
   <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+    <t xml:space="preserve">IT Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMIT Offshore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
   </si>
   <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
@@ -1287,6 +1221,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-at-paragon-4451098624</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
@@ -1317,9 +1278,6 @@
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
   </si>
   <si>
@@ -1356,103 +1314,103 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVeye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4461013504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
+    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
@@ -1607,7 +1565,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1615,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1623,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1631,7 +1589,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1016</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="10">
@@ -1703,7 +1661,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1730,44 +1688,44 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1786,63 +1744,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>472</v>
+        <v>363</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>372</v>
+        <v>458</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -1850,7 +1808,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -1858,23 +1816,23 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>367</v>
+        <v>462</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>365</v>
+        <v>463</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>476</v>
+        <v>358</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -1882,34 +1840,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>477</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>348</v>
+        <v>464</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>478</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1934,13 +1892,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2">
@@ -1951,10 +1909,10 @@
         <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1963,19 +1921,19 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>36.1</v>
+        <v>41.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -1984,67 +1942,67 @@
         <v>9.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>29.0</v>
+        <v>35.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.0</v>
+        <v>21.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.5</v>
+        <v>23.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2056,7 +2014,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2128,7 +2086,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -2160,7 +2118,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2192,7 +2150,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -2224,7 +2182,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -2256,7 +2214,7 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2288,7 +2246,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -2320,7 +2278,7 @@
         <v>51</v>
       </c>
       <c r="J8" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -2352,7 +2310,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -2384,7 +2342,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2416,7 +2374,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -2448,7 +2406,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -2480,7 +2438,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -2512,7 +2470,7 @@
         <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -2544,7 +2502,7 @@
         <v>80</v>
       </c>
       <c r="J15" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -2576,7 +2534,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -2608,7 +2566,7 @@
         <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -2640,7 +2598,7 @@
         <v>107</v>
       </c>
       <c r="J18" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2672,7 +2630,7 @@
         <v>91</v>
       </c>
       <c r="J19" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2704,7 +2662,7 @@
         <v>116</v>
       </c>
       <c r="J20" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2736,7 +2694,7 @@
         <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2768,7 +2726,7 @@
         <v>125</v>
       </c>
       <c r="J22" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -2800,7 +2758,7 @@
         <v>62</v>
       </c>
       <c r="J23" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -2832,7 +2790,7 @@
         <v>135</v>
       </c>
       <c r="J24" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2864,7 +2822,7 @@
         <v>140</v>
       </c>
       <c r="J25" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
@@ -2896,7 +2854,7 @@
         <v>146</v>
       </c>
       <c r="J26" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
@@ -2928,7 +2886,7 @@
         <v>51</v>
       </c>
       <c r="J27" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2960,7 +2918,7 @@
         <v>76</v>
       </c>
       <c r="J28" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2992,7 +2950,7 @@
         <v>158</v>
       </c>
       <c r="J29" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -3022,7 +2980,7 @@
         <v>162</v>
       </c>
       <c r="J30" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -3033,7 +2991,7 @@
         <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>43</v>
@@ -3046,40 +3004,40 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -3087,16 +3045,16 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>37</v>
@@ -3106,27 +3064,27 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>37</v>
@@ -3136,54 +3094,54 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="J34" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>43</v>
@@ -3196,13 +3154,13 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -3210,10 +3168,10 @@
         <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>43</v>
@@ -3226,24 +3184,24 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J37" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>43</v>
@@ -3256,10 +3214,10 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="J38" s="3">
         <v>3</v>
@@ -3267,10 +3225,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>160</v>
@@ -3279,31 +3237,31 @@
         <v>43</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>43</v>
@@ -3316,24 +3274,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="J40" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
@@ -3346,30 +3304,30 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="J41" s="3">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3379,18 +3337,18 @@
         <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="J42" s="3">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>160</v>
@@ -3406,21 +3364,21 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>160</v>
@@ -3436,27 +3394,27 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>48</v>
@@ -3466,27 +3424,27 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="J45" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>48</v>
@@ -3496,30 +3454,30 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="J46" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3529,21 +3487,21 @@
         <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="J47" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>43</v>
@@ -3559,27 +3517,27 @@
         <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3589,141 +3547,141 @@
         <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="J49" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>222</v>
+        <v>76</v>
       </c>
       <c r="J50" s="3">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>163</v>
+        <v>47</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>163</v>
+        <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>47</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>167</v>
+        <v>227</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>43</v>
@@ -3736,27 +3694,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>233</v>
+        <v>120</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>37</v>
@@ -3766,146 +3724,146 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>239</v>
-      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="J56" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>47</v>
+        <v>236</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>43</v>
+        <v>239</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>247</v>
+        <v>47</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="J59" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>43</v>
@@ -3918,54 +3876,54 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>245</v>
+        <v>173</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>256</v>
+        <v>76</v>
       </c>
       <c r="J61" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>43</v>
@@ -3978,21 +3936,21 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>51</v>
+        <v>254</v>
       </c>
       <c r="J62" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>160</v>
@@ -4001,34 +3959,34 @@
         <v>43</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>256</v>
+        <v>51</v>
       </c>
       <c r="J63" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>169</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>48</v>
@@ -4038,21 +3996,21 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="J64" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>47</v>
+        <v>260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>160</v>
@@ -4061,118 +4019,118 @@
         <v>43</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>169</v>
+        <v>254</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>160</v>
+        <v>265</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="J66" s="3">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>55</v>
+        <v>271</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>46</v>
+        <v>273</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>160</v>
+        <v>265</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>218</v>
+        <v>46</v>
       </c>
       <c r="J68" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>163</v>
+        <v>276</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>160</v>
@@ -4188,24 +4146,24 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>125</v>
+        <v>279</v>
       </c>
       <c r="J69" s="3">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>132</v>
@@ -4218,27 +4176,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="J70" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>182</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>132</v>
+        <v>266</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>48</v>
@@ -4248,27 +4206,27 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="J71" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>37</v>
@@ -4278,32 +4236,34 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="J72" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>163</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
@@ -4311,21 +4271,21 @@
         <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="C74" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>43</v>
@@ -4338,27 +4298,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="J74" s="3">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>296</v>
+        <v>171</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4368,145 +4328,143 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="J75" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>245</v>
+        <v>160</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>301</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>76</v>
+        <v>298</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>196</v>
+        <v>300</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>116</v>
+        <v>302</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>307</v>
-      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>195</v>
+        <v>304</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F79" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>311</v>
+        <v>171</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>160</v>
@@ -4522,100 +4480,102 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>314</v>
+        <v>46</v>
       </c>
       <c r="J80" s="3">
-        <v>87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>195</v>
+        <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="J81" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>77</v>
+        <v>315</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>212</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>212</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>160</v>
+        <v>318</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -4623,13 +4583,13 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>47</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>322</v>
+        <v>169</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>245</v>
+        <v>160</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>43</v>
@@ -4642,27 +4602,27 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="J84" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>163</v>
+        <v>322</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
@@ -4672,54 +4632,54 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>218</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>132</v>
@@ -4732,27 +4692,27 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>163</v>
+        <v>329</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>241</v>
+        <v>330</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>37</v>
@@ -4765,21 +4725,21 @@
         <v>331</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>163</v>
+        <v>332</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>172</v>
+        <v>334</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>132</v>
@@ -4792,24 +4752,24 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>334</v>
+        <v>46</v>
       </c>
       <c r="J89" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>132</v>
@@ -4822,42 +4782,42 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J90" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>307</v>
+        <v>342</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4865,218 +4825,96 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>163</v>
+        <v>344</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>182</v>
+        <v>345</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>342</v>
+        <v>173</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>172</v>
+        <v>349</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>132</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>251</v>
+        <v>352</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>348</v>
-      </c>
+      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="J94" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J96" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J97" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J98" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5171,10 +5009,6 @@
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5182,8 +5016,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5219,10 +5053,10 @@
         <v>163</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5230,18 +5064,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5249,18 +5083,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5268,18 +5102,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>232</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>268</v>
+        <v>177</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5287,18 +5121,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5306,18 +5140,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>320</v>
+        <v>212</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>160</v>
+        <v>318</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5325,18 +5159,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5344,18 +5178,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5363,30 +5197,11 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5396,7 +5211,6 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5410,15 +5224,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -5426,7 +5240,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5434,7 +5248,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>348</v>
+        <v>290</v>
       </c>
       <c r="B4" s="3">
         <v>19</v>
@@ -5445,12 +5259,12 @@
         <v>307</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -5458,7 +5272,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5466,7 +5280,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5474,7 +5288,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5482,7 +5296,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5498,7 +5312,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5506,7 +5320,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5514,7 +5328,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5522,7 +5336,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5530,7 +5344,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5543,7 +5357,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5552,7 +5366,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5565,23 +5379,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5589,7 +5403,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5597,7 +5411,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5629,7 +5443,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5637,7 +5451,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5645,7 +5459,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5653,7 +5467,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5661,7 +5475,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5669,10 +5483,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5683,23 +5497,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5791,13 +5605,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>195</v>
+        <v>142</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D8" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5805,13 +5619,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C9" s="3">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5819,13 +5633,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="C10" s="3">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5833,10 +5647,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -5847,7 +5661,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5861,7 +5675,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5903,7 +5717,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -5929,21 +5743,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3">
@@ -5951,10 +5765,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
@@ -5962,10 +5776,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -5984,7 +5798,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
@@ -5992,7 +5806,7 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -6000,7 +5814,7 @@
         <v>132</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6008,36 +5822,36 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>197</v>
+        <v>266</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>122</v>
+        <v>239</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6064,10 +5878,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6079,10 +5893,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6099,28 +5913,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>87</v>
@@ -6131,31 +5945,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
@@ -6163,31 +5977,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>402</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -6195,31 +6009,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>403</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>404</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>406</v>
+        <v>39</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -6227,31 +6041,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>407</v>
+        <v>322</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>408</v>
+        <v>323</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>410</v>
+        <v>324</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
@@ -6259,31 +6073,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>395</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>396</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="F7" s="3">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -6291,31 +6105,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>87</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6323,31 +6137,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -6355,31 +6169,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="F10" s="3">
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11">
@@ -6387,28 +6201,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F11" s="3">
         <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>46</v>
@@ -6419,28 +6233,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>432</v>
+        <v>164</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>71</v>
@@ -6451,31 +6265,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="F13" s="3">
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14">
@@ -6483,28 +6297,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="F14" s="3">
         <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>58</v>
@@ -6515,31 +6329,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>357</v>
+        <v>431</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -6547,31 +6361,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>450</v>
+        <v>173</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>451</v>
+        <v>386</v>
       </c>
       <c r="F16" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17">
@@ -6579,31 +6393,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>357</v>
+        <v>439</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>358</v>
+        <v>440</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>359</v>
+        <v>160</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>360</v>
+        <v>442</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>46</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
@@ -6611,31 +6425,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>455</v>
+        <v>332</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>456</v>
+        <v>333</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>160</v>
+        <v>334</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>458</v>
+        <v>335</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -6643,31 +6457,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>212</v>
+        <v>444</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>419</v>
+        <v>386</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>256</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -6675,31 +6489,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>463</v>
+        <v>210</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>464</v>
+        <v>160</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="F20" s="3">
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21">
@@ -6707,31 +6521,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>275</v>
+        <v>451</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>55</v>
+        <v>452</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W36.xlsx
+++ b/reports/devops-jobs-israel-2026-W36.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04T11:06:55</t>
+    <t xml:space="preserve">2026-09-06T10:47:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -264,6 +264,18 @@
     <t xml:space="preserve">2026-06-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
   </si>
   <si>
@@ -498,112 +510,538 @@
     <t xml:space="preserve">2026-08-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Viz.ai</t>
+    <t xml:space="preserve">Devops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-upwind-security-4462845714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 2115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zipher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zipher-4460024752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4461576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limy AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4462673113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4462604477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4461447149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comply365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comply365-4461182919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4463796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-matchit-4457747161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4461811560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wonderful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-upwind-security-4462845714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-group-4460483664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4462764950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- 2115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-2115-at-tsg-4461000699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zipher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zipher-4460024752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-guardio-4461576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Software Engineer - Chip Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-software-engineer-chip-design-at-nvidia-4441379111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-comblack-4462835218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comblack-4462839099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
   </si>
   <si>
     <t xml:space="preserve">Buildots</t>
@@ -612,477 +1050,120 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4458847873</t>
   </si>
   <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-glassbox-4461275027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wonderful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wonderful-4462043603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4462827885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4458893080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4461709769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4458897579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4459731662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4460455490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4461067482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4462859178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-allcloud-4462161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4461076346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Core APIs (SRE Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-engineer-core-apis-sre-focus-at-jobgether-4459756992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limy AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-limy-ai-4458855178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4462156796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-automation-engineer-at-dialog-4458883953</t>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-youcc-technologies-ltd-4459946559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37483)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37483-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4462855334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/splunk-infrastructure-engineer-at-one-technologies-4460496741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-shavit-software-4461085347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-qb-systems-ltd-4461731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPC Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-opc-energy-4459793105</t>
   </si>
   <si>
     <t xml:space="preserve">Devsecops Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4459208042</t>
   </si>
   <si>
-    <t xml:space="preserve">Sentra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sentra-4459524146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-mlops-at-directeam-4452822089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-comblack-4462839099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-comblack-4462835218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4459537006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4458846909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System &amp; Infrastructure Engineer (1007183)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-1007183-at-elad-software-systems-4461060550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37483)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37483-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4462855334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splunk Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splunk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/splunk-infrastructure-engineer-at-one-technologies-4460496741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-shavit-software-4461085347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1101,16 +1182,16 @@
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Terraform</t>
   </si>
   <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
+    <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Argo CD</t>
@@ -1119,9 +1200,6 @@
     <t xml:space="preserve">Helm</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open Roles</t>
   </si>
   <si>
@@ -1143,10 +1221,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6%</t>
+    <t xml:space="preserve">47.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1188,24 +1266,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMMIT Offshore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-systems-engineer-at-commit-offshore-4455869432</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -1221,6 +1302,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-comblack-4462803997</t>
+  </si>
+  <si>
     <t xml:space="preserve">Computer System Engineer</t>
   </si>
   <si>
@@ -1239,15 +1329,6 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-at-paragon-4451098624</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
@@ -1260,7 +1341,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18</t>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
   </si>
   <si>
     <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
@@ -1275,15 +1365,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Specialist – MENTEE</t>
   </si>
   <si>
@@ -1314,16 +1395,31 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVeye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4461013504</t>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
   </si>
   <si>
     <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
@@ -1338,6 +1434,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
@@ -1362,55 +1470,28 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
@@ -1565,7 +1646,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -1573,7 +1654,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1581,7 +1662,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1589,7 +1670,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1024</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="10">
@@ -1661,7 +1742,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -1669,7 +1750,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1688,28 +1769,28 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1717,10 +1798,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1744,55 +1825,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>485</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>459</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -1800,74 +1881,74 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>461</v>
+        <v>388</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>462</v>
+        <v>385</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>358</v>
+        <v>489</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>490</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1892,13 +1973,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2">
@@ -1906,13 +1987,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1921,88 +2002,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
-        <v>41.7</v>
+        <v>34.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.3</v>
+        <v>29.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.4</v>
+        <v>15.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2013,8 +2094,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2086,7 +2167,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -2118,7 +2199,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2231,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -2182,7 +2263,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -2214,7 +2295,7 @@
         <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2246,7 +2327,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -2278,7 +2359,7 @@
         <v>51</v>
       </c>
       <c r="J8" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -2310,7 +2391,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2342,7 +2423,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2374,12 +2455,12 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>73</v>
@@ -2394,24 +2475,24 @@
         <v>48</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>73</v>
@@ -2438,7 +2519,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -2470,7 +2551,7 @@
         <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -2499,21 +2580,21 @@
         <v>94</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J15" s="3">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>43</v>
@@ -2522,30 +2603,30 @@
         <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J16" s="3">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>43</v>
@@ -2563,21 +2644,21 @@
         <v>103</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="J17" s="3">
-        <v>39</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>43</v>
@@ -2586,19 +2667,19 @@
         <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -2606,10 +2687,10 @@
         <v>108</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>43</v>
@@ -2618,19 +2699,19 @@
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2638,10 +2719,10 @@
         <v>112</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>43</v>
@@ -2659,21 +2740,21 @@
         <v>115</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="J20" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>43</v>
@@ -2682,158 +2763,158 @@
         <v>48</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J21" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J22" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="J23" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="J24" s="3">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J25" s="3">
-        <v>31</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>43</v>
@@ -2842,30 +2923,30 @@
         <v>48</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J26" s="3">
-        <v>89</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>43</v>
@@ -2883,95 +2964,97 @@
         <v>149</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="J27" s="3">
-        <v>24</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="J28" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="J29" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="G30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>161</v>
@@ -2980,7 +3063,7 @@
         <v>162</v>
       </c>
       <c r="J30" s="3">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -3010,7 +3093,7 @@
         <v>167</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -3021,7 +3104,7 @@
         <v>169</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>43</v>
@@ -3034,27 +3117,27 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>167</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>37</v>
@@ -3064,27 +3147,27 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>37</v>
@@ -3094,54 +3177,54 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>43</v>
@@ -3157,10 +3240,10 @@
         <v>185</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
@@ -3171,7 +3254,7 @@
         <v>186</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>43</v>
@@ -3187,21 +3270,21 @@
         <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="J37" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>43</v>
@@ -3214,24 +3297,24 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>43</v>
@@ -3247,24 +3330,24 @@
         <v>192</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>37</v>
@@ -3274,24 +3357,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="J40" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>43</v>
@@ -3304,10 +3387,10 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J41" s="3">
         <v>4</v>
@@ -3315,13 +3398,13 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>43</v>
@@ -3334,24 +3417,24 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="J42" s="3">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>43</v>
@@ -3364,24 +3447,24 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>43</v>
@@ -3394,87 +3477,87 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="J45" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>47</v>
+        <v>201</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="J46" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>37</v>
@@ -3484,24 +3567,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>167</v>
+        <v>46</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>43</v>
@@ -3514,84 +3597,84 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>47</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>116</v>
+        <v>224</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>201</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>47</v>
+        <v>227</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>43</v>
@@ -3604,27 +3687,27 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>48</v>
@@ -3634,57 +3717,59 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>37</v>
@@ -3694,24 +3779,24 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J54" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>43</v>
@@ -3724,27 +3809,27 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>231</v>
+        <v>76</v>
       </c>
       <c r="J55" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3754,10 +3839,10 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="J56" s="3">
         <v>0</v>
@@ -3765,16 +3850,16 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>37</v>
@@ -3784,45 +3869,43 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="J57" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>239</v>
+        <v>36</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>240</v>
-      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3830,10 +3913,10 @@
         <v>47</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>36</v>
@@ -3846,21 +3929,21 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>165</v>
@@ -3869,31 +3952,31 @@
         <v>43</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>248</v>
+        <v>76</v>
       </c>
       <c r="J60" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>43</v>
@@ -3906,54 +3989,54 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>76</v>
+        <v>259</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>254</v>
+        <v>76</v>
       </c>
       <c r="J62" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>43</v>
@@ -3966,27 +4049,27 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>51</v>
+        <v>265</v>
       </c>
       <c r="J63" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>48</v>
@@ -3996,57 +4079,57 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="J64" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="J65" s="3">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>48</v>
@@ -4056,84 +4139,84 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="J66" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>273</v>
+        <v>46</v>
       </c>
       <c r="J67" s="3">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>266</v>
+        <v>136</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>43</v>
@@ -4146,27 +4229,27 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J69" s="3">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>48</v>
@@ -4176,116 +4259,114 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="J70" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>266</v>
+        <v>136</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>254</v>
+        <v>84</v>
       </c>
       <c r="J71" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>55</v>
+        <v>293</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>290</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>76</v>
+        <v>298</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>43</v>
@@ -4298,10 +4379,10 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J74" s="3">
         <v>4</v>
@@ -4309,16 +4390,16 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>243</v>
+        <v>174</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4328,70 +4409,70 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>46</v>
+        <v>304</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>160</v>
+        <v>273</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>43</v>
+        <v>274</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="J76" s="3">
-        <v>88</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>299</v>
+        <v>201</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>186</v>
+        <v>308</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>300</v>
+        <v>170</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>302</v>
+        <v>129</v>
       </c>
       <c r="J77" s="3">
         <v>25</v>
@@ -4399,75 +4480,75 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J78" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>47</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>307</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>43</v>
@@ -4480,116 +4561,114 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>46</v>
+        <v>317</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>312</v>
+        <v>183</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>165</v>
+        <v>319</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>313</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>76</v>
+        <v>321</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>212</v>
+        <v>323</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>167</v>
+        <v>325</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>317</v>
+        <v>47</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>212</v>
+        <v>326</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>318</v>
+        <v>165</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>169</v>
+        <v>329</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>43</v>
@@ -4597,122 +4676,124 @@
       <c r="E84" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>323</v>
+        <v>183</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="J85" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>218</v>
+        <v>334</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>327</v>
+        <v>212</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="J87" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>329</v>
+        <v>244</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>330</v>
+        <v>212</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>37</v>
@@ -4722,27 +4803,27 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>167</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>332</v>
+        <v>201</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>333</v>
+        <v>252</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>334</v>
+        <v>250</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>37</v>
@@ -4752,27 +4833,27 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>336</v>
+        <v>201</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>338</v>
+        <v>184</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>37</v>
@@ -4782,89 +4863,89 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="J90" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>342</v>
+        <v>237</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>348</v>
+        <v>183</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>349</v>
+        <v>184</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>48</v>
@@ -4877,10 +4958,10 @@
         <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="J93" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
@@ -4891,13 +4972,13 @@
         <v>352</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>178</v>
+        <v>337</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
@@ -4907,14 +4988,292 @@
         <v>353</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="J94" s="3">
-        <v>28</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J95" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J96" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J97" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J98" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J99" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J100" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J102" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J103" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J103"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5009,6 +5368,15 @@
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5016,8 +5384,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5050,32 +5418,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>165</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>166</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5083,18 +5451,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5102,18 +5470,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>232</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>177</v>
+        <v>236</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5121,18 +5489,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>315</v>
+        <v>244</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5140,18 +5508,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>316</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>317</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>318</v>
+        <v>250</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5159,18 +5527,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>319</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>329</v>
+        <v>266</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>330</v>
+        <v>267</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5178,18 +5546,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>331</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>341</v>
+        <v>289</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5197,11 +5565,30 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>343</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5211,6 +5598,7 @@
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5224,23 +5612,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>356</v>
+        <v>237</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5248,23 +5636,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>290</v>
+        <v>384</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -5272,7 +5660,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5280,15 +5668,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5296,7 +5684,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5304,7 +5692,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>128</v>
+        <v>375</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5312,15 +5700,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>363</v>
+        <v>132</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5328,15 +5716,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5344,10 +5732,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5366,7 +5754,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
@@ -5374,20 +5762,20 @@
         <v>73</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5395,7 +5783,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5403,7 +5791,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5411,7 +5799,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5419,15 +5807,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5435,7 +5823,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5443,7 +5831,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5451,7 +5839,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5459,7 +5847,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5467,7 +5855,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5475,7 +5863,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5483,7 +5871,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5504,16 +5892,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
@@ -5524,10 +5912,10 @@
         <v>73</v>
       </c>
       <c r="C2" s="3">
-        <v>23.0</v>
+        <v>27.7</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -5549,7 +5937,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C4" s="3">
         <v>10.4</v>
@@ -5563,7 +5951,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -5605,7 +5993,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -5619,13 +6007,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5633,7 +6021,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5647,13 +6035,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5661,7 +6049,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5675,7 +6063,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5689,7 +6077,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C14" s="3">
         <v>2.6</v>
@@ -5703,7 +6091,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C15" s="3">
         <v>2.6</v>
@@ -5717,7 +6105,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -5743,21 +6131,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3">
@@ -5765,10 +6153,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -5776,10 +6164,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -5798,7 +6186,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
@@ -5806,15 +6194,15 @@
         <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -5822,12 +6210,12 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5835,7 +6223,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5843,7 +6231,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5851,7 +6239,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5878,10 +6266,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -5893,10 +6281,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -5913,31 +6301,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -5945,31 +6333,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
@@ -5977,31 +6365,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>389</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>392</v>
+        <v>39</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -6009,31 +6397,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>346</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>347</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>39</v>
+        <v>348</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
@@ -6041,31 +6429,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>322</v>
+        <v>417</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>323</v>
+        <v>418</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>178</v>
+        <v>419</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -6073,28 +6461,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="F7" s="3">
         <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>76</v>
@@ -6105,31 +6493,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>401</v>
+        <v>212</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>402</v>
+        <v>174</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3">
         <v>56</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>405</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
@@ -6137,31 +6525,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>160</v>
+        <v>432</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="F9" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>175</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10">
@@ -6169,31 +6557,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="F10" s="3">
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>413</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -6201,31 +6589,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>332</v>
+        <v>440</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>415</v>
+        <v>165</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F11" s="3">
         <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
@@ -6233,31 +6621,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>418</v>
+        <v>357</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>164</v>
+        <v>444</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>165</v>
+        <v>445</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -6265,31 +6653,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="F13" s="3">
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14">
@@ -6297,28 +6685,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="F14" s="3">
         <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>58</v>
@@ -6329,31 +6717,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>431</v>
+        <v>357</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -6361,31 +6749,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>173</v>
+        <v>463</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>386</v>
+        <v>464</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>254</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
@@ -6393,31 +6781,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18">
@@ -6425,31 +6813,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>332</v>
+        <v>471</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>333</v>
+        <v>472</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="F18" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>335</v>
+        <v>474</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -6457,31 +6845,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>87</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20">
@@ -6489,31 +6877,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>447</v>
+        <v>357</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>210</v>
+        <v>358</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>160</v>
+        <v>359</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>449</v>
+        <v>360</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>254</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -6521,28 +6909,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>452</v>
+        <v>170</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>91</v>
